--- a/SuppXLS/Scen_Hydrogenupdcheap.xlsx
+++ b/SuppXLS/Scen_Hydrogenupdcheap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ee46c55b5fc2ded/Documents/Git/times-ireland-model/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78434D9D-78A7-4BD7-9045-4DAD8F079ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{78434D9D-78A7-4BD7-9045-4DAD8F079ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7EACBBF-0A62-45B7-BC7E-7D5E01BD32D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,10 +424,10 @@
     <t>ELC, BIO</t>
   </si>
   <si>
-    <t>IMPH2G*</t>
-  </si>
-  <si>
-    <t>*10</t>
+    <t>*.1</t>
+  </si>
+  <si>
+    <t>IMPH2G*,</t>
   </si>
 </sst>
 </file>
@@ -5259,10 +5259,10 @@
         <v>84</v>
       </c>
       <c r="E4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="26" t="s">
         <v>89</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>88</v>
       </c>
       <c r="H4" s="26"/>
       <c r="I4" s="26"/>
